--- a/assets/board-template.xlsx
+++ b/assets/board-template.xlsx
@@ -3035,7 +3035,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z87"/>
